--- a/data/demo/Восток заявки.xlsx
+++ b/data/demo/Восток заявки.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Волгоградский, д. 128 к 5</t>
+          <t>Город Москва, пр-кт.Волгоградский, д. 128 к 5, кв. 1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Город Москва, пер.Маяковского, д. 2</t>
+          <t>Город Москва, пер.Маяковского, д. 2, кв. 59</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Грайвороновская, д. 10 к 2</t>
+          <t>Город Москва, ул.Грайвороновская, д. 10 к 2, кв. 71</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -657,7 +657,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Михайлова, д. 14</t>
+          <t>Город Москва, ул.Михайлова, д. 14, кв. 13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Город Москва, ул.3-я Институтская, д. 5 к 2</t>
+          <t>Город Москва, ул.3-я Институтская, д. 5 к 2, кв. 36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Город Москва, ул.1-я Новокузьминская, д. 16 к 1</t>
+          <t>Город Москва, ул.1-я Новокузьминская, д. 16 к 1, кв. 11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Окская, д. 32</t>
+          <t>Город Москва, ул.Окская, д. 32, кв. 42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Юных Ленинцев, д. 84</t>
+          <t>Город Москва, ул.Юных Ленинцев, д. 84, кв. 13</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Международная, д. 28 стр. 1</t>
+          <t>Город Москва, ул.Международная, д. 28 стр. 1, кв. 186</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Новорогожская, д. 8</t>
+          <t>Город Москва, ул.Новорогожская, д. 8, кв. 18</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Чистова, д. 12</t>
+          <t>Город Москва, ул.Чистова, д. 12, кв. 61</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Паперника, д. 19</t>
+          <t>Город Москва, ул.Паперника, д. 19, кв. 35</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Окская, д. 48/2</t>
+          <t>Город Москва, ул.Окская, д. 48/2, кв. 13</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Трофимова, д. 24 к 2</t>
+          <t>Город Москва, ул.Трофимова, д. 24 к 2, кв. 26</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Город Москва, ул.1-я Дубровская, д. 6</t>
+          <t>Город Москва, ул.1-я Дубровская, д. 6, кв. 41</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Рогожский Вал, д. 2/50</t>
+          <t>Город Москва, ул.Рогожский Вал, д. 2/50, кв. 65</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Талалихина, д. 2/1 к 4</t>
+          <t>Город Москва, ул.Талалихина, д. 2/1 к 4, кв. 387</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Артюхиной, д. 20А</t>
+          <t>Город Москва, ул.Артюхиной, д. 20А, кв. 16</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Малышева, д. 13</t>
+          <t>Город Москва, ул.Малышева, д. 13, кв. 68</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Бронницкая, д. 12</t>
+          <t>Город Москва, ул.Бронницкая, д. 12, кв. 7</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Авиамоторная, д. 14</t>
+          <t>Город Москва, ул.Авиамоторная, д. 14, кв. 1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Фёдора Полетаева, д. 2 к 6</t>
+          <t>Город Москва, ул.Фёдора Полетаева, д. 2 к 6, кв. 131</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Зарайская, д. 51 к 2</t>
+          <t>Город Москва, ул.Зарайская, д. 51 к 2, кв. 67</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Саратовская, д. 14/1</t>
+          <t>Город Москва, ул.Саратовская, д. 14/1, кв. 24</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Нижегородская, д. 63</t>
+          <t>Город Москва, ул.Нижегородская, д. 63, кв. 112</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Смирновская, д. 6</t>
+          <t>Город Москва, ул.Смирновская, д. 6, кв. 35</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Нижегородская, д. 61</t>
+          <t>Город Москва, ул.Нижегородская, д. 61, кв. 30</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Зеленодольская, д. 28Б</t>
+          <t>Город Москва, ул.Зеленодольская, д. 28Б, кв. 205</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Артюхиной, д. 16</t>
+          <t>Город Москва, ул.Артюхиной, д. 16, кв. 43</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Город Москва, ул.3-я Карачаровская, д. 4 к 1</t>
+          <t>Город Москва, ул.3-я Карачаровская, д. 4 к 1, кв. 98</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Рязанский, д. 73</t>
+          <t>Город Москва, пр-кт.Рязанский, д. 73, кв. 13</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Ферганская, д. 28/7</t>
+          <t>Город Москва, ул.Ферганская, д. 28/7, кв. 244</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Самаркандский Квартал 137а, д. к5</t>
+          <t>Город Москва, б-р.Самаркандский Квартал 137а, д. к5, кв. 25</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Боровая, д. 14</t>
+          <t>Город Москва, ул.Боровая, д. 14, кв. 20</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Стройковская, д. 8</t>
+          <t>Город Москва, ул.Стройковская, д. 8, кв. 150</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Город Москва, ул.2-я Синичкина, д. 9 к 1</t>
+          <t>Город Москва, ул.2-я Синичкина, д. 9 к 1, кв. 6</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Москва, проезд Орехово-Зуевский, д. 18/8</t>
+          <t>Москва, проезд Орехово-Зуевский, д. 18/8, кв. 30</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Город Москва, пер.Большой Рогожский, д. 10 к 2</t>
+          <t>Город Москва, пер.Большой Рогожский, д. 10 к 2, кв. 73</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Машкова, д. 13 стр. 1</t>
+          <t>Город Москва, ул.Машкова, д. 13 стр. 1, кв. 15</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Город Москва, ул.11-я Текстильщиков, д. 10</t>
+          <t>Город Москва, ул.11-я Текстильщиков, д. 10, кв. 103</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Паперника, д. 18</t>
+          <t>Город Москва, ул.Паперника, д. 18, кв. 33</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Большая Калитниковская, д. 38</t>
+          <t>Город Москва, ул.Большая Калитниковская, д. 38, кв. 29</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Самаркандский Квартал 137а, д. к5</t>
+          <t>Город Москва, б-р.Самаркандский Квартал 137а, д. к5, кв. 25</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Маршала Чуйкова, д. 9 к 2</t>
+          <t>Город Москва, ул.Маршала Чуйкова, д. 9 к 2, кв. 27</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Талалихина, д. 16</t>
+          <t>Город Москва, ул.Талалихина, д. 16, кв. 74</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Город Москва, б-р.Волжский, д. 50 к 2</t>
+          <t>Город Москва, б-р.Волжский, д. 50 к 2, кв. 89</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Артюхиной, д. 3</t>
+          <t>Город Москва, ул.Артюхиной, д. 3, кв. 107</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Город Москва, проезд.Ферганский, д. 7 к 5</t>
+          <t>Город Москва, проезд.Ферганский, д. 7 к 5, кв. 18</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Земляной Вал, д. 24/30 стр. 1</t>
+          <t>Город Москва, ул.Земляной Вал, д. 24/30 стр. 1, кв. 75</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Город Москва, ул.3-я Карачаровская, д. 8 к 2</t>
+          <t>Город Москва, ул.3-я Карачаровская, д. 8 к 2, кв. 10</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Чистопольская, д. 2 к 2</t>
+          <t>Город Москва, ул.Чистопольская, д. 2 к 2, кв. 45</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Боровая, д. 12</t>
+          <t>Город Москва, ул.Боровая, д. 12, кв. 4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Красноказарменная, д. 9Б стр. 1</t>
+          <t>Город Москва, ул.Красноказарменная, д. 9Б стр. 1, кв. 126</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Сторожевая, д. 31</t>
+          <t>Город Москва, ул.Сторожевая, д. 31, кв. 44</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Новорогожская, д. 10</t>
+          <t>Город Москва, ул.Новорогожская, д. 10, кв. 56</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Нижегородская, д. 25</t>
+          <t>Город Москва, ул.Нижегородская, д. 25, кв. 385</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Город Москва, ул.Окская, д. 6 к 1</t>
+          <t>Город Москва, ул.Окская, д. 6 к 1, кв. 10</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Город Москва, пр-кт.Волгоградский, д. 97 к 1</t>
+          <t>Город Москва, пр-кт.Волгоградский, д. 97 к 1, кв. 2</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
